--- a/data/borrow_log.xlsx
+++ b/data/borrow_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -498,7 +498,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>컴퓨터공학과</t>
+          <t>컴퓨터정보공학부</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -550,7 +550,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>컴퓨터공학과</t>
+          <t>컴퓨터정보공학부</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>전자공학과</t>
+          <t>기계공학과</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -831,7 +831,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>pop'n</t>
+          <t>테스트</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -931,6 +931,178 @@
           <t>2025-09-27 23:52:53</t>
         </is>
       </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>최원서</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>01021134645</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>202121267</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>컴퓨터정보공학부</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>볼펜, 실험복</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>김세호</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2025-09-30 20:16:46</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>미반납</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>최원서</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>01021134645</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>202121267</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>컴퓨터정보공학부</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>테이프, 물티슈</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2025-09-30 17:42:51</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>신청</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>최원서</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>01021134645</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>202121267</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>컴퓨터정보공학부</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>가글, 마스크, 공학용 계산기</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>김세호</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2025-09-30 20:16:14</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>미반납</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>최원서</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>01021134645</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>202121267</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>컴퓨터정보공학부</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>인공눈물, 진통제</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>김세호</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2025-09-30 20:17:58</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>반납</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
